--- a/literature/PAPERS_TABLE.xlsx
+++ b/literature/PAPERS_TABLE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Thesis\repo\literature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69FE292-9CAB-4EC2-9A1D-D70004F8A936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB94DF1-72C8-4F2F-8DA7-2114759695BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="The papers" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Tools" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The papers'!$A$4:$AB$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The papers'!$A$4:$AC$36</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -247,9 +247,6 @@
     <t>purl.org/ontocosmetic  |  doi.org/10.1016/B978-0-443-15274-0.50316-4</t>
   </si>
   <si>
-    <t>Help a chemist design a cream that stays stable. The second paper turns that into a phone app called Formultools.</t>
-  </si>
-  <si>
     <t>Cosmetic formulators, not shoppers</t>
   </si>
   <si>
@@ -2021,9 +2018,6 @@
   </si>
   <si>
     <t xml:space="preserve">  7ad ba3ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Only the skincare ontologies, side by side with us. The three green rows are the whole thesis.</t>
   </si>
   <si>
     <t>Moe &amp; Aung
@@ -3307,12 +3301,18 @@
   <si>
     <t>All tools</t>
   </si>
+  <si>
+    <t>Journal Rank</t>
+  </si>
+  <si>
+    <t>Help a chemist design a cream tha+L6+M7+L6+M7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3495,8 +3495,22 @@
       <color rgb="FF6B4E9B"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF2166A5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3593,6 +3607,12 @@
         <fgColor rgb="FFF4F1EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -3674,7 +3694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
@@ -3886,6 +3906,12 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4189,7 +4215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4198,30 +4224,31 @@
     <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="38" customWidth="1"/>
-    <col min="12" max="12" width="44" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
-    <col min="15" max="16" width="26" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="46" customWidth="1"/>
-    <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="40" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
-    <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="24" max="24" width="46" customWidth="1"/>
-    <col min="25" max="25" width="48" customWidth="1"/>
-    <col min="26" max="26" width="34" customWidth="1"/>
-    <col min="27" max="27" width="44" customWidth="1"/>
-    <col min="28" max="28" width="66" customWidth="1"/>
+    <col min="7" max="7" width="21.26953125" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="38" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="16" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="46" customWidth="1"/>
+    <col min="21" max="21" width="42" customWidth="1"/>
+    <col min="22" max="22" width="40" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="38" customWidth="1"/>
+    <col min="25" max="25" width="46" customWidth="1"/>
+    <col min="26" max="26" width="48" customWidth="1"/>
+    <col min="27" max="27" width="34" customWidth="1"/>
+    <col min="28" max="28" width="44" customWidth="1"/>
+    <col min="29" max="29" width="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
@@ -4252,9 +4279,10 @@
       <c r="Z1" s="49"/>
       <c r="AA1" s="49"/>
       <c r="AB1" s="49"/>
-    </row>
-    <row r="2" spans="1:28" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC1" s="49"/>
+    </row>
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="51" t="s">
         <v>1</v>
       </c>
@@ -4268,37 +4296,38 @@
       <c r="I3" s="49"/>
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="49"/>
+      <c r="M3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="49"/>
-      <c r="N3" s="51" t="s">
+      <c r="N3" s="49"/>
+      <c r="O3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="49"/>
+      <c r="Q3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="49"/>
       <c r="R3" s="49"/>
       <c r="S3" s="49"/>
       <c r="T3" s="49"/>
       <c r="U3" s="49"/>
       <c r="V3" s="49"/>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="49"/>
+      <c r="X3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="49"/>
       <c r="Y3" s="49"/>
-      <c r="Z3" s="50" t="s">
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="52" t="s">
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="52" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -4318,73 +4347,76 @@
         <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>36</v>
       </c>
@@ -4415,8 +4447,9 @@
       <c r="Z5" s="49"/>
       <c r="AA5" s="49"/>
       <c r="AB5" s="49"/>
-    </row>
-    <row r="6" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC5" s="49"/>
+    </row>
+    <row r="6" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
@@ -4435,74 +4468,75 @@
       <c r="F6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="U6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="W6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="X6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="Y6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Z6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Z6" s="3" t="s">
+      <c r="AA6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AA6" s="3" t="s">
+      <c r="AB6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AB6" s="9" t="s">
+      <c r="AC6" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" ht="178" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>63</v>
       </c>
@@ -4521,506 +4555,512 @@
       <c r="F7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="J7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="K7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="L7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="M7" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="N7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="O7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="P7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="Q7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="R7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="S7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="T7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="U7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="V7" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="U7" s="10" t="s">
+      <c r="W7" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="V7" s="14" t="s">
+      <c r="X7" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="W7" s="10" t="s">
+      <c r="Y7" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="Z7" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="AA7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="Z7" s="10" t="s">
+      <c r="AB7" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="10" t="s">
+      <c r="AC7" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AB7" s="9" t="s">
+    </row>
+    <row r="8" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="J8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="M8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="W8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="V8" s="7" t="s">
+      <c r="X8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="Y8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="AB8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AC8" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="AB8" s="9" t="s">
+    </row>
+    <row r="9" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="I9" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="J9" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="K9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="L9" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="M9" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="N9" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="O9" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="P9" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="Q9" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="R9" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="10" t="s">
+      <c r="S9" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="S9" s="10" t="s">
+      <c r="U9" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="V9" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="U9" s="10" t="s">
+      <c r="W9" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="V9" s="12" t="s">
+      <c r="X9" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="W9" s="10" t="s">
+      <c r="Y9" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="X9" s="10" t="s">
+      <c r="Z9" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="Y9" s="10" t="s">
+      <c r="AA9" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="Z9" s="10" t="s">
+      <c r="AB9" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="AA9" s="10" t="s">
+      <c r="AC9" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AB9" s="9" t="s">
+    </row>
+    <row r="10" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="I10" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="J10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="L10" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="M10" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="U10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="V10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="V10" s="7" t="s">
+      <c r="X10" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="Y10" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="Z10" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="AA10" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="AB10" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AC10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="AB10" s="9" t="s">
+    </row>
+    <row r="11" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="I11" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="J11" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="L11" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="M11" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="N11" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="O11" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="P11" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="Q11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="R11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="S11" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="R11" s="10" t="s">
+      <c r="T11" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="U11" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="V11" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="S11" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="T11" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="U11" s="10" t="s">
+      <c r="W11" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y11" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="V11" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="W11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="X11" s="10" t="s">
+      <c r="Z11" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="Y11" s="10" t="s">
+      <c r="AA11" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="Z11" s="10" t="s">
+      <c r="AB11" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="AA11" s="10" t="s">
+      <c r="AC11" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="AB11" s="9" t="s">
+    </row>
+    <row r="12" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="M12" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="P12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>157</v>
+        <v>51</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="W12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="X12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="Y12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z12" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Y12" s="3" t="s">
+      <c r="AA12" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="Z12" s="3" t="s">
+      <c r="AB12" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AA12" s="3" t="s">
+      <c r="AC12" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="AB12" s="9" t="s">
+    </row>
+    <row r="13" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="53" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="53" t="s">
-        <v>199</v>
       </c>
       <c r="B13" s="49"/>
       <c r="C13" s="49"/>
@@ -5049,698 +5089,707 @@
       <c r="Z13" s="49"/>
       <c r="AA13" s="49"/>
       <c r="AB13" s="49"/>
-    </row>
-    <row r="14" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC13" s="49"/>
+    </row>
+    <row r="14" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="I14" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="J14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="M14" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="W14" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="V14" s="14" t="s">
+      <c r="X14" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AC14" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="AB14" s="9" t="s">
+    </row>
+    <row r="15" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="B15" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="I15" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="J15" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="L15" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="R15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="V15" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="X15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z15" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB15" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC15" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="T15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="V15" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="W15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="X15" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z15" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA15" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="AB15" s="9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="D16" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E16" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="I16" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="J16" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="L16" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="M16" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="O16" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="P16" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="Q16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="S16" s="3" t="s">
+      <c r="U16" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="T16" s="3" t="s">
+      <c r="V16" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="U16" s="3" t="s">
+      <c r="W16" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="V16" s="14" t="s">
+      <c r="X16" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="W16" s="3" t="s">
+      <c r="Y16" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="X16" s="3" t="s">
+      <c r="Z16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC16" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="Y16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB16" s="9" t="s">
+    </row>
+    <row r="17" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="B17" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="I17" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="J17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="I17" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J17" s="10" t="s">
+      <c r="L17" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="M17" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="N17" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="O17" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="P17" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q17" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="O17" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="P17" s="10" t="s">
+      <c r="R17" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T17" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="U17" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="V17" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="W17" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="Q17" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R17" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="T17" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="U17" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="V17" s="14" t="s">
+      <c r="X17" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="W17" s="10" t="s">
+      <c r="Y17" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="X17" s="10" t="s">
+      <c r="Z17" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="Y17" s="10" t="s">
+      <c r="AA17" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="Z17" s="10" t="s">
+      <c r="AB17" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="AA17" s="10" t="s">
+      <c r="AC17" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="AB17" s="9" t="s">
+    </row>
+    <row r="18" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="I18" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="J18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="L18" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q18" s="3" t="s">
+      <c r="T18" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="U18" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="W18" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC18" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="V18" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB18" s="9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="H19" s="12" t="s">
+      <c r="K19" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="L19" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J19" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N19" s="10" t="s">
+      <c r="Q19" s="10" t="s">
         <v>318</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q19" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="R19" s="10" t="s">
         <v>51</v>
       </c>
       <c r="S19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="V19" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="X19" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y19" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z19" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="T19" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="U19" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="W19" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="X19" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y19" s="10" t="s">
+      <c r="AA19" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="Z19" s="10" t="s">
+      <c r="AB19" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="AA19" s="10" t="s">
+      <c r="AC19" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="AB19" s="9" t="s">
+    </row>
+    <row r="20" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="D20" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="I20" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="J20" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="L20" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="M20" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="Q20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="W20" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="V20" s="7" t="s">
+      <c r="X20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y20" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="X20" s="3" t="s">
+      <c r="Z20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA20" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z20" s="3" t="s">
+      <c r="AB20" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="AA20" s="3" t="s">
+      <c r="AC20" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="AB20" s="9" t="s">
+    </row>
+    <row r="21" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+      <c r="B21" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="G21" s="10"/>
+      <c r="H21" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="I21" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="J21" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" s="13" t="s">
+      <c r="M21" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="N21" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="M21" s="10" t="s">
+      <c r="O21" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="N21" s="10" t="s">
+      <c r="P21" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="Q21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="R21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="U21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="V21" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="W21" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="P21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="T21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="U21" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="V21" s="12" t="s">
+      <c r="X21" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="W21" s="10" t="s">
+      <c r="Y21" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z21" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="X21" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Y21" s="10" t="s">
+      <c r="AA21" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="Z21" s="10" t="s">
+      <c r="AB21" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="AA21" s="10" t="s">
+      <c r="AC21" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="AB21" s="9" t="s">
+    </row>
+    <row r="22" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="55" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="55" t="s">
-        <v>362</v>
       </c>
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
@@ -5769,612 +5818,620 @@
       <c r="Z22" s="49"/>
       <c r="AA22" s="49"/>
       <c r="AB22" s="49"/>
-    </row>
-    <row r="23" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC22" s="49"/>
+    </row>
+    <row r="23" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="C23" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="G23" s="10"/>
+      <c r="H23" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="I23" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="J23" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="K23" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="L23" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="M23" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="N23" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="M23" s="10" t="s">
+      <c r="O23" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="N23" s="10" t="s">
+      <c r="P23" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="O23" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>319</v>
-      </c>
       <c r="Q23" s="10" t="s">
-        <v>51</v>
+        <v>318</v>
       </c>
       <c r="R23" s="10" t="s">
         <v>51</v>
       </c>
       <c r="S23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="T23" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="U23" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="T23" s="10" t="s">
+      <c r="V23" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="U23" s="10" t="s">
+      <c r="W23" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="V23" s="12" t="s">
+      <c r="X23" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="W23" s="10" t="s">
+      <c r="Y23" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="X23" s="10" t="s">
+      <c r="Z23" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="Y23" s="10" t="s">
+      <c r="AA23" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="Z23" s="10" t="s">
+      <c r="AB23" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="AA23" s="10" t="s">
+      <c r="AC23" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="AB23" s="9" t="s">
+    </row>
+    <row r="24" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="I24" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="J24" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="L24" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="M24" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="T24" s="3" t="s">
+      <c r="V24" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="U24" s="3" t="s">
+      <c r="W24" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="V24" s="14" t="s">
+      <c r="X24" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="W24" s="3" t="s">
+      <c r="Y24" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="X24" s="3" t="s">
+      <c r="Z24" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="Y24" s="3" t="s">
+      <c r="AA24" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="Z24" s="3" t="s">
+      <c r="AB24" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="AA24" s="3" t="s">
+      <c r="AC24" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="AB24" s="9" t="s">
+    </row>
+    <row r="25" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+      <c r="B25" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="F25" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="G25" s="10"/>
+      <c r="H25" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="I25" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="J25" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="K25" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="L25" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="M25" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="N25" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="O25" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="P25" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="O25" s="10" t="s">
+      <c r="Q25" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="R25" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S25" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T25" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="P25" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q25" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R25" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S25" s="10" t="s">
+      <c r="U25" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="V25" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="W25" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="U25" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="V25" s="12" t="s">
+      <c r="X25" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="W25" s="10" t="s">
+      <c r="Y25" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="X25" s="10" t="s">
+      <c r="Z25" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="Y25" s="10" t="s">
+      <c r="AA25" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="Z25" s="10" t="s">
+      <c r="AB25" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="AA25" s="10" t="s">
+      <c r="AC25" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="AB25" s="9" t="s">
+    </row>
+    <row r="26" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="E26" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3"/>
+      <c r="H26" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="J26" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="L26" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="M26" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="N26" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="P26" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="O26" s="3" t="s">
+      <c r="Q26" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="P26" s="3" t="s">
+      <c r="R26" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="S26" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="T26" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="S26" s="3" t="s">
+      <c r="U26" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="T26" s="3" t="s">
+      <c r="V26" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="U26" s="3" t="s">
+      <c r="W26" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="V26" s="7" t="s">
+      <c r="X26" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="W26" s="3" t="s">
+      <c r="Y26" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="X26" s="3" t="s">
+      <c r="Z26" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="Y26" s="3" t="s">
+      <c r="AA26" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="Z26" s="3" t="s">
+      <c r="AB26" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="AA26" s="3" t="s">
+      <c r="AC26" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="AB26" s="9" t="s">
+    </row>
+    <row r="27" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
+      <c r="B27" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>462</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="D27" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="I27" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="J27" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="K27" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="L27" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="K27" s="13" t="s">
+      <c r="M27" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="N27" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="M27" s="10" t="s">
+      <c r="O27" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="N27" s="10" t="s">
+      <c r="P27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="R27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="U27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="V27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="W27" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="O27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="T27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="U27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="V27" s="12" t="s">
+      <c r="X27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z27" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="W27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="X27" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y27" s="10" t="s">
+      <c r="AA27" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="Z27" s="10" t="s">
+      <c r="AB27" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="AA27" s="10" t="s">
+      <c r="AC27" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="AB27" s="9" t="s">
+    </row>
+    <row r="28" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="D28" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="E28" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="I28" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="J28" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="L28" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="M28" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="N28" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="O28" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="R28" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V28" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="T28" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="U28" s="3" t="s">
+      <c r="W28" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="X28" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="V28" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="W28" s="3" t="s">
+      <c r="Y28" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="X28" s="3" t="s">
+      <c r="Z28" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="Y28" s="3" t="s">
+      <c r="AA28" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="Z28" s="3" t="s">
+      <c r="AB28" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="AA28" s="3" t="s">
+      <c r="AC28" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="AB28" s="9" t="s">
+    </row>
+    <row r="29" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+      <c r="B29" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="D29" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="I29" s="15" t="s">
         <v>507</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="J29" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" s="10" t="s">
+      <c r="L29" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="M29" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="N29" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="M29" s="10" t="s">
+      <c r="O29" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="N29" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="O29" s="10" t="s">
+      <c r="P29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="P29" s="10" t="s">
-        <v>319</v>
-      </c>
       <c r="Q29" s="10" t="s">
-        <v>51</v>
+        <v>318</v>
       </c>
       <c r="R29" s="10" t="s">
         <v>51</v>
       </c>
       <c r="S29" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="T29" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="U29" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="V29" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="T29" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="U29" s="10" t="s">
+      <c r="W29" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="V29" s="12" t="s">
+      <c r="X29" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z29" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="W29" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="X29" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y29" s="10" t="s">
+      <c r="AA29" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="Z29" s="10" t="s">
+      <c r="AB29" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="AA29" s="10" t="s">
+      <c r="AC29" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="AB29" s="9" t="s">
+    </row>
+    <row r="30" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="56" t="s">
         <v>520</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
-        <v>521</v>
       </c>
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
@@ -6403,538 +6460,545 @@
       <c r="Z30" s="49"/>
       <c r="AA30" s="49"/>
       <c r="AB30" s="49"/>
-    </row>
-    <row r="31" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC30" s="49"/>
+    </row>
+    <row r="31" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="D31" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="I31" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="J31" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="K31" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L31" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="J31" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K31" s="13" t="s">
+      <c r="M31" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="N31" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="O31" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="P31" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="Q31" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="P31" s="10" t="s">
+      <c r="R31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="U31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="V31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="W31" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="Q31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="T31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="V31" s="12" t="s">
+      <c r="X31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z31" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA31" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="W31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="X31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y31" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z31" s="10" t="s">
+      <c r="AB31" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="AA31" s="10" t="s">
+      <c r="AC31" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="AB31" s="9" t="s">
+    </row>
+    <row r="32" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="B32" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>540</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C32" s="21" t="s">
+      <c r="D32" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="E32" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="I32" s="15" t="s">
         <v>545</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="J32" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="L32" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="M32" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="N32" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="O32" s="3" t="s">
+      <c r="P32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="Q32" s="3" t="s">
-        <v>51</v>
+        <v>318</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="T32" s="3" t="s">
+      <c r="V32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="W32" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y32" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="V32" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="X32" s="3" t="s">
+      <c r="Z32" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="Y32" s="3" t="s">
+      <c r="AA32" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="Z32" s="3" t="s">
+      <c r="AB32" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="AA32" s="3" t="s">
+      <c r="AC32" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="AB32" s="9" t="s">
+    </row>
+    <row r="33" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="B33" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C33" s="21" t="s">
+      <c r="D33" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="I33" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="J33" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J33" s="10" t="s">
+      <c r="L33" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="K33" s="13" t="s">
+      <c r="M33" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="N33" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="O33" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="P33" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="Q33" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="P33" s="10" t="s">
+      <c r="R33" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="Q33" s="10" t="s">
+      <c r="S33" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="R33" s="10" t="s">
+      <c r="T33" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="S33" s="10" t="s">
+      <c r="U33" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="V33" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="T33" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="U33" s="10" t="s">
+      <c r="W33" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="V33" s="14" t="s">
+      <c r="X33" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="W33" s="10" t="s">
+      <c r="Y33" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="X33" s="10" t="s">
+      <c r="Z33" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="Y33" s="10" t="s">
+      <c r="AA33" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="Z33" s="10" t="s">
+      <c r="AB33" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="AA33" s="10" t="s">
+      <c r="AC33" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="AB33" s="9" t="s">
+    </row>
+    <row r="34" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="B34" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>584</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C34" s="21" t="s">
+      <c r="D34" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="E34" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="I34" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="J34" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="L34" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="M34" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="N34" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="O34" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="M34" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="N34" s="3" t="s">
+      <c r="P34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="W34" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y34" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z34" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="O34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="V34" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y34" s="3" t="s">
+      <c r="AA34" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="Z34" s="3" t="s">
+      <c r="AB34" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="AA34" s="3" t="s">
+      <c r="AC34" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="AB34" s="9" t="s">
+    </row>
+    <row r="35" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="B35" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>599</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C35" s="21" t="s">
+      <c r="D35" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="E35" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="I35" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="J35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J35" s="10" t="s">
+      <c r="L35" s="13" t="s">
         <v>605</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="M35" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="N35" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="M35" s="10" t="s">
+      <c r="O35" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="N35" s="10" t="s">
+      <c r="P35" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="S35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="T35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="U35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="V35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="W35" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="R35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="S35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="T35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="U35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="V35" s="12" t="s">
+      <c r="X35" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y35" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="W35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="X35" s="10" t="s">
+      <c r="Z35" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="Y35" s="10" t="s">
+      <c r="AA35" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="Z35" s="10" t="s">
+      <c r="AB35" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="AA35" s="10" t="s">
+      <c r="AC35" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="AB35" s="9" t="s">
+    </row>
+    <row r="36" spans="1:29" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C36" s="21" t="s">
+      <c r="D36" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="E36" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="I36" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="J36" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J36" s="3" t="s">
+      <c r="L36" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="M36" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="N36" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="O36" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="P36" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="O36" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="Q36" s="3" t="s">
-        <v>51</v>
+        <v>238</v>
       </c>
       <c r="R36" s="3" t="s">
         <v>51</v>
       </c>
       <c r="S36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V36" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="T36" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="U36" s="3" t="s">
+      <c r="W36" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="X36" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="V36" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="W36" s="3" t="s">
+      <c r="Y36" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="X36" s="3" t="s">
+      <c r="Z36" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="Y36" s="3" t="s">
+      <c r="AA36" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="Z36" s="3" t="s">
+      <c r="AB36" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="AA36" s="3" t="s">
+      <c r="AC36" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="AB36" s="9" t="s">
-        <v>635</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB36" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC36" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="12">
-    <mergeCell ref="A13:AB13"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="A22:AB22"/>
-    <mergeCell ref="A30:AB30"/>
-    <mergeCell ref="A5:AB5"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AB3"/>
-    <mergeCell ref="P3:V3"/>
+    <mergeCell ref="A13:AC13"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="A22:AC22"/>
+    <mergeCell ref="A30:AC30"/>
+    <mergeCell ref="A5:AC5"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="AC3"/>
+    <mergeCell ref="Q3:W3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6942,7 +7006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6952,7 +7016,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -6964,174 +7028,192 @@
       <c r="I1" s="49"/>
       <c r="J1" s="49"/>
     </row>
-    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="48" t="s">
+    <row r="2" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22"/>
+      <c r="B4" s="23" t="s">
+        <v>636</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>637</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-    </row>
-    <row r="3" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
-      <c r="B5" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>638</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="E4" s="23" t="s">
         <v>639</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="F4" s="23" t="s">
         <v>640</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>641</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="H4" s="23" t="s">
         <v>642</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="I4" s="23" t="s">
         <v>643</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="J4" s="24" t="s">
         <v>644</v>
       </c>
-      <c r="I5" s="23" t="s">
+    </row>
+    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>646</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>648</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>647</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>648</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="E6" s="26" t="s">
         <v>650</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>649</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>649</v>
+      <c r="B6" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>653</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="F7" s="28" t="s">
         <v>655</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>655</v>
+      <c r="B7" s="26" t="s">
+        <v>656</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>657</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>658</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>658</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>651</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>657</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>659</v>
-      </c>
-      <c r="F8" s="26" t="s">
         <v>660</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>660</v>
-      </c>
-      <c r="H8" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>653</v>
+      <c r="B8" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>662</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>664</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>667</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>662</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>663</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>664</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>663</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>665</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>666</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="I9" s="29" t="s">
+      <c r="A9" s="31" t="s">
         <v>669</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>651</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>652</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>651</v>
       </c>
       <c r="J9" s="27" t="s">
         <v>670</v>
@@ -7142,293 +7224,260 @@
         <v>671</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>672</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J10" s="27" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="31" t="s">
-        <v>673</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>653</v>
+        <v>675</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>676</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>678</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>675</v>
+        <v>651</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>651</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
-        <v>677</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>678</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>679</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E12" s="33" t="s">
+      <c r="A12" s="25" t="s">
         <v>680</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>653</v>
+      <c r="B12" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>666</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>681</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>681</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>668</v>
+      <c r="D13" s="30" t="s">
+        <v>653</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>683</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>684</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>653</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>685</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>653</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>509</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>684</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>655</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>685</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>686</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>655</v>
-      </c>
-      <c r="H14" s="26" t="s">
         <v>687</v>
       </c>
-      <c r="I14" s="30" t="s">
-        <v>655</v>
+      <c r="B14" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>688</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>689</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>690</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>691</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>692</v>
       </c>
       <c r="J14" s="27" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>689</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>690</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>691</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>692</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>693</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="I15" s="29" t="s">
         <v>694</v>
       </c>
+      <c r="B15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>695</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>696</v>
+      </c>
       <c r="J15" s="27" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="B16" s="30" t="s">
+        <v>698</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>699</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F16" s="28" t="s">
         <v>653</v>
       </c>
-      <c r="C16" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>697</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="H16" s="30" t="s">
-        <v>653</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>698</v>
+      <c r="G16" s="29" t="s">
+        <v>701</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>702</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>703</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
-        <v>700</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="I17" s="29" t="s">
         <v>705</v>
       </c>
+      <c r="B17" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>707</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>709</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>711</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>712</v>
+      </c>
+      <c r="I17" s="26" t="s">
+        <v>713</v>
+      </c>
       <c r="J17" s="27" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>707</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>708</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>709</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>710</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>711</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>712</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>713</v>
-      </c>
-      <c r="H18" s="26" t="s">
         <v>714</v>
       </c>
-      <c r="I18" s="26" t="s">
-        <v>715</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>716</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7455,7 +7504,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -7486,7 +7535,7 @@
     <row r="3" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="63" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
@@ -7500,31 +7549,31 @@
     </row>
     <row r="6" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>718</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="E6" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>719</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="G6" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>720</v>
       </c>
-      <c r="E6" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="F6" s="34" t="s">
+      <c r="I6" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="J6" s="37" t="s">
         <v>721</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>722</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.35">
@@ -7541,7 +7590,7 @@
     </row>
     <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="63" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C9" s="49"/>
       <c r="D9" s="49"/>
@@ -7555,101 +7604,101 @@
     </row>
     <row r="10" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="70" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C10" s="49"/>
       <c r="D10" s="61" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="62" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G10" s="49"/>
       <c r="H10" s="64" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="I10" s="49"/>
     </row>
     <row r="11" spans="1:12" ht="63.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="60" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="68" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E11" s="49"/>
       <c r="F11" s="59" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G11" s="49"/>
       <c r="H11" s="69" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="I11" s="49"/>
     </row>
     <row r="12" spans="1:12" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="60" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="68" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E12" s="49"/>
       <c r="F12" s="59" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G12" s="49"/>
       <c r="H12" s="69" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="I12" s="49"/>
     </row>
     <row r="13" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="60" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="68" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="59" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G13" s="49"/>
       <c r="H13" s="69" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="I13" s="49"/>
     </row>
     <row r="14" spans="1:12" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="60" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="68" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="59" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G14" s="49"/>
       <c r="H14" s="69" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="I14" s="49"/>
     </row>
     <row r="15" spans="1:12" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="60" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="68" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E15" s="49"/>
       <c r="F15" s="59"/>
@@ -7659,11 +7708,11 @@
     </row>
     <row r="16" spans="1:12" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="60" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C16" s="49"/>
       <c r="D16" s="68" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="59"/>
@@ -7673,11 +7722,11 @@
     </row>
     <row r="17" spans="2:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="60" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="68" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E17" s="49"/>
       <c r="F17" s="59"/>
@@ -7687,7 +7736,7 @@
     </row>
     <row r="18" spans="2:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="60" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="68"/>
@@ -7699,7 +7748,7 @@
     </row>
     <row r="19" spans="2:11" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="66" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="49"/>
@@ -7713,7 +7762,7 @@
     </row>
     <row r="21" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="63" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -7727,36 +7776,36 @@
     </row>
     <row r="22" spans="2:11" ht="147" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38" t="s">
+        <v>752</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>753</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="F22" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="G22" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="H22" s="40" t="s">
         <v>755</v>
       </c>
-      <c r="E22" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="F22" s="39" t="s">
+      <c r="I22" s="35" t="s">
+        <v>717</v>
+      </c>
+      <c r="J22" s="41" t="s">
         <v>756</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>757</v>
-      </c>
-      <c r="I22" s="35" t="s">
-        <v>719</v>
-      </c>
-      <c r="J22" s="41" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="66" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -7770,7 +7819,7 @@
     </row>
     <row r="25" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="63" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C25" s="49"/>
       <c r="D25" s="49"/>
@@ -7784,17 +7833,17 @@
     </row>
     <row r="26" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="67" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C26" s="49"/>
       <c r="D26" s="67" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E26" s="49"/>
       <c r="F26" s="49"/>
       <c r="G26" s="49"/>
       <c r="H26" s="67" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="I26" s="49"/>
       <c r="J26" s="49"/>
@@ -7802,17 +7851,17 @@
     </row>
     <row r="27" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="65" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="58" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
       <c r="G27" s="49"/>
       <c r="H27" s="58" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I27" s="49"/>
       <c r="J27" s="49"/>
@@ -7820,17 +7869,17 @@
     </row>
     <row r="28" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="65" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C28" s="49"/>
       <c r="D28" s="58" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49"/>
       <c r="H28" s="58" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="I28" s="49"/>
       <c r="J28" s="49"/>
@@ -7838,17 +7887,17 @@
     </row>
     <row r="29" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="65" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="58" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
       <c r="G29" s="49"/>
       <c r="H29" s="58" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="I29" s="49"/>
       <c r="J29" s="49"/>
@@ -7856,17 +7905,17 @@
     </row>
     <row r="30" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="65" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="58" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E30" s="49"/>
       <c r="F30" s="49"/>
       <c r="G30" s="49"/>
       <c r="H30" s="58" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
@@ -7874,17 +7923,17 @@
     </row>
     <row r="31" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="65" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C31" s="49"/>
       <c r="D31" s="58" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E31" s="49"/>
       <c r="F31" s="49"/>
       <c r="G31" s="49"/>
       <c r="H31" s="58" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="I31" s="49"/>
       <c r="J31" s="49"/>
@@ -7892,17 +7941,17 @@
     </row>
     <row r="32" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="65" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C32" s="49"/>
       <c r="D32" s="58" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="49"/>
       <c r="G32" s="49"/>
       <c r="H32" s="58" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="I32" s="49"/>
       <c r="J32" s="49"/>
@@ -7910,7 +7959,7 @@
     </row>
     <row r="33" spans="2:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="66" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
@@ -8012,7 +8061,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -8033,27 +8082,27 @@
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>783</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="71" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
@@ -8063,147 +8112,147 @@
     </row>
     <row r="7" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="42" t="s">
+        <v>792</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>806</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="42" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="44" t="s">
         <v>810</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="G11" s="3" t="s">
         <v>811</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="42" t="s">
+        <v>812</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>816</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="42" t="s">
+        <v>817</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>821</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="71" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="49"/>
@@ -8213,107 +8262,107 @@
     </row>
     <row r="15" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="42" t="s">
+        <v>823</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>828</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="42" t="s">
+        <v>828</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="42" t="s">
+        <v>833</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>838</v>
-      </c>
-      <c r="F17" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="42" t="s">
+        <v>838</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>843</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="42" t="s">
+        <v>843</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="45" t="s">
         <v>847</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="G19" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="F19" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="71" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -8323,67 +8372,67 @@
     </row>
     <row r="21" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="42" t="s">
+        <v>850</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>854</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="42" t="s">
+        <v>855</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="F22" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>860</v>
-      </c>
-      <c r="F22" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="42" t="s">
+        <v>860</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>864</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="71" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C24" s="49"/>
       <c r="D24" s="49"/>
@@ -8393,107 +8442,107 @@
     </row>
     <row r="25" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="F25" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="42" t="s">
+        <v>871</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>876</v>
-      </c>
-      <c r="F26" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="42" t="s">
+        <v>876</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="F27" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="F27" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="42" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="F28" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>885</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="42" t="s">
+        <v>885</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="F29" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>889</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>890</v>
-      </c>
-      <c r="F29" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="71" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -8503,87 +8552,87 @@
     </row>
     <row r="31" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="42" t="s">
+        <v>891</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>894</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>895</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="42" t="s">
+        <v>895</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="F32" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="F32" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="42" t="s">
+        <v>900</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="E33" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="F33" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>904</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>905</v>
-      </c>
-      <c r="F33" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="42" t="s">
+        <v>905</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="F34" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>910</v>
-      </c>
-      <c r="F34" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="71" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
@@ -8593,147 +8642,147 @@
     </row>
     <row r="36" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="42" t="s">
+        <v>911</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="F36" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>916</v>
-      </c>
-      <c r="F36" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="42" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F37" s="46" t="s">
         <v>918</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F37" s="46" t="s">
-        <v>920</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>922</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="F38" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="42" t="s">
+        <v>923</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="E39" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="F39" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>927</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>928</v>
-      </c>
-      <c r="F39" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="42" t="s">
+        <v>928</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="F40" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="F40" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="42" t="s">
+        <v>933</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="F41" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>937</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="F41" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="42" t="s">
+        <v>938</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="E42" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="F42" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>942</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>943</v>
-      </c>
-      <c r="F42" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="71" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C43" s="49"/>
       <c r="D43" s="49"/>
@@ -8743,127 +8792,127 @@
     </row>
     <row r="44" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="42" t="s">
+        <v>944</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="8" t="s">
         <v>947</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="F44" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>949</v>
-      </c>
-      <c r="F44" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="42" t="s">
+        <v>949</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="E45" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="F45" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>953</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>954</v>
-      </c>
-      <c r="F45" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="42" t="s">
+        <v>954</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>956</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="F46" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>959</v>
-      </c>
-      <c r="F46" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="F47" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>963</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>964</v>
-      </c>
-      <c r="F47" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="42" t="s">
+        <v>964</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>966</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="E48" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>967</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>966</v>
-      </c>
-      <c r="F48" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="42" t="s">
+        <v>968</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="E49" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="F49" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>972</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="71" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
@@ -8873,107 +8922,107 @@
     </row>
     <row r="51" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="42" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="F51" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>977</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>978</v>
-      </c>
-      <c r="F51" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="42" t="s">
+        <v>978</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="E52" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="F52" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>982</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>983</v>
-      </c>
-      <c r="F52" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="42" t="s">
+        <v>983</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="F53" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G53" s="3" t="s">
         <v>987</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>988</v>
-      </c>
-      <c r="F53" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="42" t="s">
+        <v>988</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="F54" s="47" t="s">
         <v>992</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="G54" s="3" t="s">
         <v>993</v>
-      </c>
-      <c r="F54" s="47" t="s">
-        <v>994</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="42" t="s">
+        <v>994</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="F55" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>999</v>
-      </c>
-      <c r="F55" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="71" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C56" s="49"/>
       <c r="D56" s="49"/>
@@ -8983,202 +9032,202 @@
     </row>
     <row r="57" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="42" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="F57" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>1004</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="42" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="E58" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="F58" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>1009</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="42" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="E59" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="F59" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>1014</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F59" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="60" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="42" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="E60" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="F60" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>1019</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="42" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>1022</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="E61" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="F61" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>1024</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F61" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="42" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="E62" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="F62" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>1029</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F62" s="44" t="s">
-        <v>812</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="42" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="E63" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="F63" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F63" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="42" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>1037</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="E64" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="F64" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>1039</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="42" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="E65" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="F65" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>1044</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F65" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="42" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="E66" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="F66" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>1049</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F66" s="45" t="s">
-        <v>849</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>1051</v>
       </c>
     </row>
   </sheetData>
